--- a/dataset_control_tabla.xlsx
+++ b/dataset_control_tabla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arlin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7CB552-0D16-4612-805F-DEBB9BBAC91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87090A5A-4A0D-4BAA-9923-44533CA44B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2830" yWindow="2830" windowWidth="14500" windowHeight="7320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-101" yWindow="-101" windowWidth="19536" windowHeight="10352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="demographics" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -34,9 +34,6 @@
     <t>center</t>
   </si>
   <si>
-    <t>Edad en días (ADNI/MID)</t>
-  </si>
-  <si>
     <t>audit child</t>
   </si>
   <si>
@@ -362,6 +359,12 @@
   </si>
   <si>
     <t>Validat: f</t>
+  </si>
+  <si>
+    <t>Edad en días (ADNI)</t>
+  </si>
+  <si>
+    <t>Edad en días (MID)</t>
   </si>
 </sst>
 </file>
@@ -668,6 +671,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -684,27 +689,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="1">
         <v>5331</v>
@@ -721,16 +729,16 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E3" s="1">
         <v>5451</v>
@@ -747,16 +755,16 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E4" s="1">
         <v>5141</v>
@@ -773,16 +781,16 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E5" s="6">
         <v>5255</v>
@@ -799,16 +807,16 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="1">
         <v>5220</v>
@@ -825,16 +833,16 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E7" s="1">
         <v>5145</v>
@@ -851,16 +859,16 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>5017</v>
@@ -877,16 +885,16 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="E9" s="1">
         <v>5463</v>
@@ -903,16 +911,16 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1">
         <v>4929</v>
@@ -929,16 +937,16 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="E11" s="1">
         <v>5444</v>
@@ -955,16 +963,16 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E12" s="1">
         <v>5155</v>
@@ -981,16 +989,16 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="C13" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1">
         <v>5333</v>
@@ -1007,16 +1015,16 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1">
         <v>5377</v>
@@ -1033,16 +1041,16 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="9">
         <v>5303</v>
@@ -1059,16 +1067,16 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="C16" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1">
         <v>5175</v>
@@ -1085,16 +1093,16 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="C17" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1">
         <v>5200</v>
@@ -1111,16 +1119,16 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" s="1">
         <v>5343</v>
@@ -1137,16 +1145,16 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="C19" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1">
         <v>5294</v>
@@ -1163,16 +1171,16 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="C20" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" s="1">
         <v>5104</v>
@@ -1189,16 +1197,16 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="E21" s="1">
         <v>5622</v>
@@ -1215,16 +1223,16 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="C22" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1">
         <v>5183</v>
@@ -1241,16 +1249,16 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="C23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E23" s="1">
         <v>5249</v>
@@ -1267,16 +1275,16 @@
     </row>
     <row r="24" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="C24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="E24" s="1">
         <v>5126</v>
@@ -1293,16 +1301,16 @@
     </row>
     <row r="25" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="C25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E25" s="1">
         <v>5437</v>
@@ -1319,16 +1327,16 @@
     </row>
     <row r="26" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="1">
         <v>5376</v>
@@ -1345,16 +1353,16 @@
     </row>
     <row r="27" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="C27" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1">
         <v>5477</v>
@@ -1371,16 +1379,16 @@
     </row>
     <row r="28" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="C28" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1">
         <v>5257</v>
@@ -1397,16 +1405,16 @@
     </row>
     <row r="29" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="C29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1">
         <v>5327</v>
@@ -1423,16 +1431,16 @@
     </row>
     <row r="30" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="C30" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1">
         <v>5371</v>
@@ -1449,16 +1457,16 @@
     </row>
     <row r="31" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="C31" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1">
         <v>5354</v>
@@ -1475,16 +1483,16 @@
     </row>
     <row r="32" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="C32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E32" s="1">
         <v>5433</v>
@@ -1501,16 +1509,16 @@
     </row>
     <row r="33" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="C33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E33" s="1">
         <v>5316</v>
@@ -1527,16 +1535,16 @@
     </row>
     <row r="34" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="C34" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34" s="1">
         <v>5353</v>
@@ -1553,16 +1561,16 @@
     </row>
     <row r="35" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="C35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E35" s="1">
         <v>5343</v>
@@ -1579,16 +1587,16 @@
     </row>
     <row r="36" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1">
         <v>5329</v>
@@ -1605,16 +1613,16 @@
     </row>
     <row r="37" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="C37" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E37" s="1">
         <v>5380</v>
@@ -1631,16 +1639,16 @@
     </row>
     <row r="38" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="C38" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" s="1">
         <v>5448</v>
@@ -1657,16 +1665,16 @@
     </row>
     <row r="39" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="C39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E39" s="1">
         <v>5425</v>
@@ -1683,16 +1691,16 @@
     </row>
     <row r="40" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="C40" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1">
         <v>5476</v>
@@ -1709,16 +1717,16 @@
     </row>
     <row r="41" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="C41" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" s="1">
         <v>5413</v>
@@ -1735,16 +1743,16 @@
     </row>
     <row r="42" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="C42" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E42" s="1">
         <v>5453</v>
@@ -1761,16 +1769,16 @@
     </row>
     <row r="43" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="C43" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E43" s="1">
         <v>5097</v>
@@ -1787,16 +1795,16 @@
     </row>
     <row r="44" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="C44" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" s="1">
         <v>5274</v>
@@ -1813,16 +1821,16 @@
     </row>
     <row r="45" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="C45" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" s="1">
         <v>5081</v>
@@ -1839,16 +1847,16 @@
     </row>
     <row r="46" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>106</v>
-      </c>
       <c r="C46" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E46" s="1">
         <v>5095</v>
@@ -1865,16 +1873,16 @@
     </row>
     <row r="47" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E47" s="1">
         <v>5154</v>
@@ -1891,16 +1899,16 @@
     </row>
     <row r="48" spans="1:8" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>110</v>
-      </c>
       <c r="C48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E48" s="1">
         <v>5394</v>
@@ -1917,16 +1925,16 @@
     </row>
     <row r="49" spans="1:11" ht="12.6" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="C49" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E49" s="1">
         <v>5455</v>
@@ -1943,7 +1951,7 @@
     </row>
     <row r="51" spans="1:11" ht="12.6" x14ac:dyDescent="0.25">
       <c r="K51" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
